--- a/SuppXLS/Demands/Dem_Alloc+Series.xlsx
+++ b/SuppXLS/Demands/Dem_Alloc+Series.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261020-v02\SuppXLS\Demands\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\Demands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B3FCC8-9E9B-4258-855B-4E891E4BEB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EB107F-6C73-487F-B56C-D9F99AAE051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="2" r:id="rId1"/>

--- a/SuppXLS/Demands/Dem_Alloc+Series.xlsx
+++ b/SuppXLS/Demands/Dem_Alloc+Series.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\Demands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EB107F-6C73-487F-B56C-D9F99AAE051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3637EC4-B335-452D-9E6E-F40B40F5A22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="2" r:id="rId1"/>
